--- a/research/traditional_assets/database/data/sweden/sweden_coal_related_energy.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_coal_related_energy.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.385</v>
+        <v>-0.0238</v>
       </c>
       <c r="G2">
-        <v>-1018.571428571429</v>
+        <v>-12.86940966010733</v>
       </c>
       <c r="H2">
-        <v>-1088.571428571429</v>
+        <v>-13.55992844364937</v>
       </c>
       <c r="I2">
-        <v>-1121.428571428571</v>
+        <v>-9.838998211091234</v>
       </c>
       <c r="J2">
-        <v>-1121.428571428571</v>
+        <v>-9.838998211091234</v>
       </c>
       <c r="K2">
-        <v>-9.02</v>
+        <v>-5.77</v>
       </c>
       <c r="L2">
-        <v>-1288.571428571428</v>
+        <v>-10.32200357781753</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5.84</v>
+        <v>0.773</v>
       </c>
       <c r="V2">
-        <v>0.09012345679012346</v>
+        <v>0.02415625</v>
       </c>
       <c r="W2">
-        <v>-14.76268412438625</v>
+        <v>-1.037769784172662</v>
       </c>
       <c r="X2">
-        <v>0.06217548677893862</v>
+        <v>0.12248313531049</v>
       </c>
       <c r="Y2">
-        <v>-14.82485961116519</v>
+        <v>-1.160252919483152</v>
       </c>
       <c r="Z2">
-        <v>0.0009984310369419483</v>
+        <v>0.09133986928104575</v>
       </c>
       <c r="AA2">
-        <v>-1.119669091427756</v>
+        <v>-0.8986928104575161</v>
       </c>
       <c r="AB2">
-        <v>0.05858248707113632</v>
+        <v>0.1190557691057124</v>
       </c>
       <c r="AC2">
-        <v>-1.178251578498893</v>
+        <v>-1.017748579563229</v>
       </c>
       <c r="AD2">
-        <v>6.4</v>
+        <v>1.73</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>6.4</v>
+        <v>1.73</v>
       </c>
       <c r="AG2">
-        <v>0.5600000000000005</v>
+        <v>0.957</v>
       </c>
       <c r="AH2">
-        <v>0.0898876404494382</v>
+        <v>0.05128965312777943</v>
       </c>
       <c r="AI2">
-        <v>0.5351170568561873</v>
+        <v>0.2746031746031746</v>
       </c>
       <c r="AJ2">
-        <v>0.008567931456548356</v>
+        <v>0.02903783718178232</v>
       </c>
       <c r="AK2">
-        <v>0.09150326797385629</v>
+        <v>0.173149990953501</v>
       </c>
       <c r="AL2">
-        <v>1.21</v>
+        <v>0.278</v>
       </c>
       <c r="AM2">
-        <v>1.193</v>
+        <v>0.274</v>
       </c>
       <c r="AN2">
-        <v>-0.8236808236808237</v>
+        <v>-0.3180147058823529</v>
       </c>
       <c r="AO2">
-        <v>-6.487603305785123</v>
+        <v>-19.7841726618705</v>
       </c>
       <c r="AP2">
-        <v>-0.07207207207207214</v>
+        <v>-0.1759191176470588</v>
       </c>
       <c r="AQ2">
-        <v>-6.580050293378038</v>
+        <v>-20.07299270072993</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.385</v>
+        <v>-0.0238</v>
       </c>
       <c r="G3">
-        <v>-1018.571428571429</v>
+        <v>-12.86940966010733</v>
       </c>
       <c r="H3">
-        <v>-1088.571428571429</v>
+        <v>-13.55992844364937</v>
       </c>
       <c r="I3">
-        <v>-1121.428571428571</v>
+        <v>-9.838998211091234</v>
       </c>
       <c r="J3">
-        <v>-1121.428571428571</v>
+        <v>-9.838998211091234</v>
       </c>
       <c r="K3">
-        <v>-9.02</v>
+        <v>-5.77</v>
       </c>
       <c r="L3">
-        <v>-1288.571428571428</v>
+        <v>-10.32200357781753</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5.84</v>
+        <v>0.773</v>
       </c>
       <c r="V3">
-        <v>0.09012345679012346</v>
+        <v>0.02415625</v>
       </c>
       <c r="W3">
-        <v>-14.76268412438625</v>
+        <v>-1.037769784172662</v>
       </c>
       <c r="X3">
-        <v>0.06217548677893862</v>
+        <v>0.12248313531049</v>
       </c>
       <c r="Y3">
-        <v>-14.82485961116519</v>
+        <v>-1.160252919483152</v>
       </c>
       <c r="Z3">
-        <v>0.0009984310369419483</v>
+        <v>0.09133986928104575</v>
       </c>
       <c r="AA3">
-        <v>-1.119669091427756</v>
+        <v>-0.8986928104575161</v>
       </c>
       <c r="AB3">
-        <v>0.05858248707113632</v>
+        <v>0.1190557691057124</v>
       </c>
       <c r="AC3">
-        <v>-1.178251578498893</v>
+        <v>-1.017748579563229</v>
       </c>
       <c r="AD3">
-        <v>6.4</v>
+        <v>1.73</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>6.4</v>
+        <v>1.73</v>
       </c>
       <c r="AG3">
-        <v>0.5600000000000005</v>
+        <v>0.957</v>
       </c>
       <c r="AH3">
-        <v>0.0898876404494382</v>
+        <v>0.05128965312777943</v>
       </c>
       <c r="AI3">
-        <v>0.5351170568561873</v>
+        <v>0.2746031746031746</v>
       </c>
       <c r="AJ3">
-        <v>0.008567931456548356</v>
+        <v>0.02903783718178232</v>
       </c>
       <c r="AK3">
-        <v>0.09150326797385629</v>
+        <v>0.173149990953501</v>
       </c>
       <c r="AL3">
-        <v>1.21</v>
+        <v>0.278</v>
       </c>
       <c r="AM3">
-        <v>1.193</v>
+        <v>0.274</v>
       </c>
       <c r="AN3">
-        <v>-0.8236808236808237</v>
+        <v>-0.3180147058823529</v>
       </c>
       <c r="AO3">
-        <v>-6.487603305785123</v>
+        <v>-19.7841726618705</v>
       </c>
       <c r="AP3">
-        <v>-0.07207207207207214</v>
+        <v>-0.1759191176470588</v>
       </c>
       <c r="AQ3">
-        <v>-6.580050293378038</v>
+        <v>-20.07299270072993</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/sweden/sweden_coal_related_energy.xlsx
+++ b/research/traditional_assets/database/data/sweden/sweden_coal_related_energy.xlsx
@@ -588,34 +588,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0238</v>
+        <v>0.0584</v>
       </c>
       <c r="G2">
-        <v>-12.86940966010733</v>
+        <v>-6.91923076923077</v>
       </c>
       <c r="H2">
-        <v>-13.55992844364937</v>
+        <v>-7.423076923076922</v>
       </c>
       <c r="I2">
-        <v>-9.838998211091234</v>
+        <v>-8.628205128205128</v>
       </c>
       <c r="J2">
-        <v>-9.838998211091234</v>
+        <v>-8.628205128205128</v>
       </c>
       <c r="K2">
-        <v>-5.77</v>
+        <v>-7.35</v>
       </c>
       <c r="L2">
-        <v>-10.32200357781753</v>
+        <v>-9.423076923076922</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.159</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.01127659574468085</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>-0.02163265306122449</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,76 +627,79 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>0.159</v>
+      </c>
+      <c r="T2">
+        <v>1</v>
       </c>
       <c r="U2">
-        <v>0.773</v>
+        <v>0.375</v>
       </c>
       <c r="V2">
-        <v>0.02415625</v>
+        <v>0.02659574468085106</v>
       </c>
       <c r="W2">
-        <v>-1.037769784172662</v>
+        <v>-1.608315098468271</v>
       </c>
       <c r="X2">
-        <v>0.12248313531049</v>
+        <v>0.09938875273278892</v>
       </c>
       <c r="Y2">
-        <v>-1.160252919483152</v>
+        <v>-1.70770385120106</v>
       </c>
       <c r="Z2">
-        <v>0.09133986928104575</v>
+        <v>0.1411253844762077</v>
       </c>
       <c r="AA2">
-        <v>-0.8986928104575161</v>
+        <v>-1.217658766057536</v>
       </c>
       <c r="AB2">
-        <v>0.1190557691057124</v>
+        <v>0.08726138322836628</v>
       </c>
       <c r="AC2">
-        <v>-1.017748579563229</v>
+        <v>-1.304920149285902</v>
       </c>
       <c r="AD2">
-        <v>1.73</v>
+        <v>3.82</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.73</v>
+        <v>3.82</v>
       </c>
       <c r="AG2">
-        <v>0.957</v>
+        <v>3.445</v>
       </c>
       <c r="AH2">
-        <v>0.05128965312777943</v>
+        <v>0.2131696428571429</v>
       </c>
       <c r="AI2">
-        <v>0.2746031746031746</v>
+        <v>0.9037142181215994</v>
       </c>
       <c r="AJ2">
-        <v>0.02903783718178232</v>
+        <v>0.1963522371045882</v>
       </c>
       <c r="AK2">
-        <v>0.173149990953501</v>
+        <v>0.8943406022845275</v>
       </c>
       <c r="AL2">
-        <v>0.278</v>
+        <v>0.657</v>
       </c>
       <c r="AM2">
-        <v>0.274</v>
+        <v>0.623</v>
       </c>
       <c r="AN2">
-        <v>-0.3180147058823529</v>
+        <v>-0.5727136431784108</v>
       </c>
       <c r="AO2">
-        <v>-19.7841726618705</v>
+        <v>-10.24353120243531</v>
       </c>
       <c r="AP2">
-        <v>-0.1759191176470588</v>
+        <v>-0.5164917541229385</v>
       </c>
       <c r="AQ2">
-        <v>-20.07299270072993</v>
+        <v>-10.80256821829856</v>
       </c>
     </row>
     <row r="3">
@@ -716,34 +719,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0238</v>
+        <v>0.0584</v>
       </c>
       <c r="G3">
-        <v>-12.86940966010733</v>
+        <v>-6.91923076923077</v>
       </c>
       <c r="H3">
-        <v>-13.55992844364937</v>
+        <v>-7.423076923076922</v>
       </c>
       <c r="I3">
-        <v>-9.838998211091234</v>
+        <v>-8.628205128205128</v>
       </c>
       <c r="J3">
-        <v>-9.838998211091234</v>
+        <v>-8.628205128205128</v>
       </c>
       <c r="K3">
-        <v>-5.77</v>
+        <v>-7.35</v>
       </c>
       <c r="L3">
-        <v>-10.32200357781753</v>
+        <v>-9.423076923076922</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>0.159</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.01127659574468085</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0.02163265306122449</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -755,76 +758,79 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.159</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0.773</v>
+        <v>0.375</v>
       </c>
       <c r="V3">
-        <v>0.02415625</v>
+        <v>0.02659574468085106</v>
       </c>
       <c r="W3">
-        <v>-1.037769784172662</v>
+        <v>-1.608315098468271</v>
       </c>
       <c r="X3">
-        <v>0.12248313531049</v>
+        <v>0.09938875273278892</v>
       </c>
       <c r="Y3">
-        <v>-1.160252919483152</v>
+        <v>-1.70770385120106</v>
       </c>
       <c r="Z3">
-        <v>0.09133986928104575</v>
+        <v>0.1411253844762077</v>
       </c>
       <c r="AA3">
-        <v>-0.8986928104575161</v>
+        <v>-1.217658766057536</v>
       </c>
       <c r="AB3">
-        <v>0.1190557691057124</v>
+        <v>0.08726138322836628</v>
       </c>
       <c r="AC3">
-        <v>-1.017748579563229</v>
+        <v>-1.304920149285902</v>
       </c>
       <c r="AD3">
-        <v>1.73</v>
+        <v>3.82</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>1.73</v>
+        <v>3.82</v>
       </c>
       <c r="AG3">
-        <v>0.957</v>
+        <v>3.445</v>
       </c>
       <c r="AH3">
-        <v>0.05128965312777943</v>
+        <v>0.2131696428571429</v>
       </c>
       <c r="AI3">
-        <v>0.2746031746031746</v>
+        <v>0.9037142181215994</v>
       </c>
       <c r="AJ3">
-        <v>0.02903783718178232</v>
+        <v>0.1963522371045882</v>
       </c>
       <c r="AK3">
-        <v>0.173149990953501</v>
+        <v>0.8943406022845275</v>
       </c>
       <c r="AL3">
-        <v>0.278</v>
+        <v>0.657</v>
       </c>
       <c r="AM3">
-        <v>0.274</v>
+        <v>0.623</v>
       </c>
       <c r="AN3">
-        <v>-0.3180147058823529</v>
+        <v>-0.5727136431784108</v>
       </c>
       <c r="AO3">
-        <v>-19.7841726618705</v>
+        <v>-10.24353120243531</v>
       </c>
       <c r="AP3">
-        <v>-0.1759191176470588</v>
+        <v>-0.5164917541229385</v>
       </c>
       <c r="AQ3">
-        <v>-20.07299270072993</v>
+        <v>-10.80256821829856</v>
       </c>
     </row>
   </sheetData>
